--- a/Team-Data/2013-14/4-6-2013-14.xlsx
+++ b/Team-Data/2013-14/4-6-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.447</v>
+        <v>0.44</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>9.5</v>
@@ -691,7 +758,7 @@
         <v>25.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O2" t="n">
         <v>16.9</v>
@@ -706,13 +773,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
         <v>39.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
@@ -721,25 +788,25 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB2" t="n">
         <v>101.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
@@ -784,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
@@ -933,7 +1000,7 @@
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>24</v>
@@ -963,7 +1030,7 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1115,7 +1182,7 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1297,7 +1364,7 @@
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
@@ -1357,7 +1424,7 @@
         <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
@@ -1515,19 +1582,19 @@
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
@@ -1774,43 +1841,43 @@
         <v>83.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="R8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
         <v>13.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.3</v>
@@ -1822,16 +1889,16 @@
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.1</v>
+        <v>105.2</v>
       </c>
       <c r="AC8" t="n">
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1876,10 +1943,10 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1888,16 +1955,16 @@
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>0.429</v>
+        <v>0.434</v>
       </c>
       <c r="H9" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J9" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.448</v>
@@ -1962,34 +2029,34 @@
         <v>8.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.72</v>
       </c>
       <c r="R9" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S9" t="n">
         <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
@@ -1998,25 +2065,25 @@
         <v>5.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" t="n">
         <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.1</v>
+        <v>103.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,10 +2101,10 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2055,13 +2122,13 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2070,13 +2137,13 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2243,7 +2310,7 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -2264,7 +2331,7 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -2299,49 +2366,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
         <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.378</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
         <v>34.3</v>
@@ -2350,7 +2417,7 @@
         <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2362,7 +2429,7 @@
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z11" t="n">
         <v>21.7</v>
@@ -2371,13 +2438,13 @@
         <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>103.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,16 +2456,16 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2419,7 +2486,7 @@
         <v>19</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,13 +2495,13 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2446,13 +2513,13 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -2481,64 +2548,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.473</v>
       </c>
       <c r="L12" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N12" t="n">
         <v>0.355</v>
       </c>
       <c r="O12" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P12" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="Q12" t="n">
         <v>0.707</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S12" t="n">
         <v>34</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V12" t="n">
         <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.6</v>
@@ -2553,37 +2620,37 @@
         <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.1</v>
+        <v>106.8</v>
       </c>
       <c r="AC12" t="n">
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
@@ -2607,19 +2674,19 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.679</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2693,28 +2760,28 @@
         <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
         <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="T13" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
         <v>15.1</v>
@@ -2723,25 +2790,25 @@
         <v>6.8</v>
       </c>
       <c r="X13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
         <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2753,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2771,19 +2838,19 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>1</v>
@@ -2795,16 +2862,16 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
@@ -2813,10 +2880,10 @@
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.705</v>
+        <v>0.701</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>8.4</v>
@@ -2875,25 +2942,25 @@
         <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
         <v>28.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.731</v>
+        <v>0.733</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U14" t="n">
         <v>24.5</v>
@@ -2902,31 +2969,31 @@
         <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.8</v>
+        <v>107.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2962,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2977,10 +3044,10 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>0.325</v>
+        <v>0.329</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3051,16 +3118,16 @@
         <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P15" t="n">
         <v>22.5</v>
@@ -3069,10 +3136,10 @@
         <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T15" t="n">
         <v>41.2</v>
@@ -3081,13 +3148,13 @@
         <v>24.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
@@ -3099,13 +3166,13 @@
         <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3129,7 +3196,7 @@
         <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3138,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3165,13 +3232,13 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
         <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>0.584</v>
+        <v>0.592</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.461</v>
@@ -3239,7 +3306,7 @@
         <v>13.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
         <v>15.1</v>
@@ -3248,16 +3315,16 @@
         <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R16" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
@@ -3281,34 +3348,34 @@
         <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3332,7 +3399,7 @@
         <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3347,7 +3414,7 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3391,55 +3458,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
         <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
         <v>22.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>7.7</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="U17" t="n">
         <v>22.8</v>
@@ -3448,7 +3515,7 @@
         <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X17" t="n">
         <v>4.6</v>
@@ -3457,22 +3524,22 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
         <v>103</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3484,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,19 +3736,19 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>8</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>0.416</v>
+        <v>0.421</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
@@ -3955,10 +4022,10 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
         <v>5.8</v>
@@ -3982,10 +4049,10 @@
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
@@ -4003,19 +4070,19 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA20" t="n">
         <v>20.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4030,13 +4097,13 @@
         <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4057,7 +4124,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4069,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -4119,34 +4186,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
         <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J21" t="n">
         <v>82.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.372</v>
@@ -4155,7 +4222,7 @@
         <v>15.1</v>
       </c>
       <c r="P21" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q21" t="n">
         <v>0.756</v>
@@ -4164,7 +4231,7 @@
         <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
         <v>40.5</v>
@@ -4182,7 +4249,7 @@
         <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -4191,16 +4258,16 @@
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
@@ -4209,16 +4276,16 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4239,7 +4306,7 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4254,7 +4321,7 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
@@ -4266,7 +4333,7 @@
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" t="n">
         <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0.724</v>
+        <v>0.733</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4322,40 +4389,40 @@
         <v>82.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P22" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q22" t="n">
         <v>0.806</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S22" t="n">
         <v>34.2</v>
       </c>
       <c r="T22" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
@@ -4367,19 +4434,19 @@
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,16 +4458,16 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL22" t="n">
         <v>14</v>
@@ -4415,13 +4482,13 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4442,10 +4509,10 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4618,7 +4685,7 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>22</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
         <v>9.4</v>
@@ -4877,25 +4944,25 @@
         <v>25.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P25" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S25" t="n">
         <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
         <v>19.2</v>
@@ -4916,16 +4983,16 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.7</v>
+        <v>105.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4940,22 +5007,22 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4967,7 +5034,7 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,13 +5046,13 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -4997,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.641</v>
+        <v>0.636</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5050,25 +5117,25 @@
         <v>87</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R26" t="n">
         <v>12.5</v>
@@ -5101,13 +5168,13 @@
         <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.6</v>
+        <v>106.7</v>
       </c>
       <c r="AC26" t="n">
         <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,31 +5186,31 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5176,10 +5243,10 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,31 +5296,31 @@
         <v>36.9</v>
       </c>
       <c r="J27" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
         <v>6.1</v>
       </c>
       <c r="M27" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O27" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P27" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.761</v>
       </c>
       <c r="R27" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S27" t="n">
         <v>32.3</v>
@@ -5277,40 +5344,40 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>28</v>
@@ -5331,13 +5398,13 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5352,10 +5419,10 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5364,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.779</v>
+        <v>0.776</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5411,16 +5478,16 @@
         <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N28" t="n">
         <v>0.4</v>
@@ -5429,10 +5496,10 @@
         <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="R28" t="n">
         <v>9.199999999999999</v>
@@ -5441,7 +5508,7 @@
         <v>34.1</v>
       </c>
       <c r="T28" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U28" t="n">
         <v>25.3</v>
@@ -5465,13 +5532,13 @@
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.6</v>
+        <v>105.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5540,10 +5607,10 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5677,7 +5744,7 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5689,22 +5756,22 @@
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT29" t="n">
         <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -5757,34 +5824,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>0.312</v>
+        <v>0.316</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.442</v>
       </c>
       <c r="L30" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N30" t="n">
         <v>0.35</v>
@@ -5793,7 +5860,7 @@
         <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.747</v>
@@ -5805,37 +5872,37 @@
         <v>30.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7.1</v>
+        <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5847,7 +5914,7 @@
         <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>29</v>
@@ -5859,10 +5926,10 @@
         <v>24</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN30" t="n">
         <v>24</v>
@@ -5883,13 +5950,13 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>27</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6038,7 +6105,7 @@
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>16</v>
@@ -6047,7 +6114,7 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
@@ -6056,10 +6123,10 @@
         <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6077,7 +6144,7 @@
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-6-2013-14</t>
+          <t>2014-04-06</t>
         </is>
       </c>
     </row>
